--- a/docs/oc-regiones/alimentos/atacama.xlsx
+++ b/docs/oc-regiones/alimentos/atacama.xlsx
@@ -1570,7 +1570,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3188,7 +3192,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5241,7 +5249,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6184,7 +6196,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7127,7 +7143,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7688,7 +7708,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8001,7 +8025,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8871,7 +8899,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10391,7 +10423,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11013,7 +11049,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11257,7 +11297,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13013,7 +13057,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13074,7 +13122,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13135,7 +13187,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14265,7 +14321,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14391,7 +14451,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15277,7 +15341,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15521,7 +15589,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15891,7 +15963,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16078,7 +16154,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17476,7 +17556,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +18824,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19813,7 +19901,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20756,7 +20848,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21065,7 +21161,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22272,7 +22372,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23081,7 +23185,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23646,7 +23754,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23833,7 +23945,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25284,7 +25400,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25532,7 +25652,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26036,7 +26160,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +26859,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27491,7 +27623,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28121,7 +28257,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28682,7 +28822,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30068,7 +30212,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30942,7 +31090,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31068,7 +31220,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32198,7 +32354,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32320,7 +32480,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32511,7 +32675,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33714,7 +33882,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34588,7 +34760,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35214,7 +35390,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35966,7 +36146,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36649,7 +36833,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37023,7 +37211,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37588,7 +37780,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38588,7 +38784,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39226,7 +39426,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39848,7 +40052,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40730,7 +40938,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41291,7 +41503,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42612,7 +42828,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42799,7 +43019,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43299,7 +43523,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43551,7 +43779,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43864,7 +44096,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44368,7 +44604,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45693,7 +45933,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45941,7 +46185,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L725" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46510,7 +46758,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48266,7 +48518,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K762" t="inlineStr"/>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L762" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49205,7 +49461,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K777" t="inlineStr"/>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L777" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49331,7 +49591,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K779" t="inlineStr"/>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L779" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49961,7 +50225,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K789" t="inlineStr"/>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L789" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50713,7 +50981,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K801" t="inlineStr"/>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L801" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52168,7 +52440,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K824" t="inlineStr"/>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L824" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52615,7 +52891,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K831" t="inlineStr"/>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L831" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53420,7 +53700,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K844" t="inlineStr"/>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L844" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53481,7 +53765,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K845" t="inlineStr"/>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L845" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53668,7 +53956,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K848" t="inlineStr"/>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L848" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55314,7 +55606,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K874" t="inlineStr"/>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L874" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55879,7 +56175,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K883" t="inlineStr"/>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L883" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56005,7 +56305,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K885" t="inlineStr"/>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L885" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56253,7 +56557,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K889" t="inlineStr"/>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L889" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56826,7 +57134,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K898" t="inlineStr"/>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L898" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57070,7 +57382,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K902" t="inlineStr"/>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L902" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57570,7 +57886,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K910" t="inlineStr"/>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L910" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59216,7 +59536,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K936" t="inlineStr"/>
+      <c r="K936" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L936" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59277,7 +59601,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K937" t="inlineStr"/>
+      <c r="K937" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L937" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60094,7 +60422,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K950" t="inlineStr"/>
+      <c r="K950" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L950" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60277,7 +60609,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K953" t="inlineStr"/>
+      <c r="K953" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L953" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61484,7 +61820,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K972" t="inlineStr"/>
+      <c r="K972" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L972" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62106,7 +62446,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K982" t="inlineStr"/>
+      <c r="K982" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L982" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63423,7 +63767,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1003" t="inlineStr"/>
+      <c r="K1003" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1003" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63923,7 +64271,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1011" t="inlineStr"/>
+      <c r="K1011" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1011" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64045,7 +64397,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1013" t="inlineStr"/>
+      <c r="K1013" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1013" t="inlineStr">
         <is>
           <t>USD</t>
